--- a/StructureDefinition-vuns-context.xlsx
+++ b/StructureDefinition-vuns-context.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T18:27:09+01:00</t>
+    <t>2026-10-15T09:50:14+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
